--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121699106</v>
+        <v>121713395</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568829</v>
+        <v>568807</v>
       </c>
       <c r="R2" t="n">
-        <v>6434927</v>
+        <v>6434948</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +752,9 @@
           <t>2024-12-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +778,136 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121699106</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>568829</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6434927</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett större område men fler mindre i direkt närhet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121699106</v>
+        <v>121713395</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568829</v>
+        <v>568807</v>
       </c>
       <c r="R2" t="n">
-        <v>6434927</v>
+        <v>6434948</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,24 +752,9 @@
           <t>2024-12-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett större område men fler mindre i direkt närhet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121713395</v>
+        <v>121699106</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,41 +797,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568807</v>
+        <v>568829</v>
       </c>
       <c r="R3" t="n">
-        <v>6434948</v>
+        <v>6434927</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,9 +866,24 @@
           <t>2024-12-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett större område men fler mindre i direkt närhet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121713395</v>
+        <v>121699106</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568807</v>
+        <v>568829</v>
       </c>
       <c r="R2" t="n">
-        <v>6434948</v>
+        <v>6434927</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,9 +760,24 @@
           <t>2024-12-21</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett större område men fler mindre i direkt närhet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,6 +786,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121699106</v>
+        <v>121713395</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,49 +821,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568829</v>
+        <v>568807</v>
       </c>
       <c r="R3" t="n">
-        <v>6434927</v>
+        <v>6434948</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,24 +882,9 @@
           <t>2024-12-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett större område men fler mindre i direkt närhet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +893,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121699106</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121713395</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121699106</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121713395</v>
       </c>
       <c r="B3" t="n">
-        <v>94903</v>
+        <v>94905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262266</v>
+        <v>122262138</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>94840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,31 +1055,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R5" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,6 +1127,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262169</v>
+        <v>122262123</v>
       </c>
       <c r="B6" t="n">
         <v>57390</v>
@@ -1193,14 +1190,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R6" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262138</v>
+        <v>122262149</v>
       </c>
       <c r="B7" t="n">
-        <v>94840</v>
+        <v>90799</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1268,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568911</v>
+        <v>568834</v>
       </c>
       <c r="R7" t="n">
-        <v>6434976</v>
+        <v>6434943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262149</v>
+        <v>122262266</v>
       </c>
       <c r="B8" t="n">
-        <v>90799</v>
+        <v>57744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1382,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1462,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262123</v>
+        <v>122262169</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1524,14 +1524,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568908</v>
+        <v>568766</v>
       </c>
       <c r="R9" t="n">
-        <v>6434963</v>
+        <v>6434978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262138</v>
+        <v>122262149</v>
       </c>
       <c r="B5" t="n">
-        <v>94840</v>
+        <v>90809</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568911</v>
+        <v>568834</v>
       </c>
       <c r="R5" t="n">
-        <v>6434976</v>
+        <v>6434943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262123</v>
+        <v>122262266</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,20 +1165,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,23 +1191,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568908</v>
+        <v>568766</v>
       </c>
       <c r="R6" t="n">
-        <v>6434963</v>
+        <v>6434978</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262149</v>
+        <v>122262169</v>
       </c>
       <c r="B7" t="n">
-        <v>90799</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,34 +1279,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R7" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1355,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262266</v>
+        <v>122262138</v>
       </c>
       <c r="B8" t="n">
-        <v>57744</v>
+        <v>94850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1389,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R8" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,6 +1461,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262169</v>
+        <v>122262123</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1524,14 +1524,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R9" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262149</v>
+        <v>122262138</v>
       </c>
       <c r="B5" t="n">
-        <v>90809</v>
+        <v>94850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568834</v>
+        <v>568911</v>
       </c>
       <c r="R5" t="n">
-        <v>6434943</v>
+        <v>6434976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262266</v>
+        <v>122262123</v>
       </c>
       <c r="B6" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,20 +1158,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,23 +1184,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R6" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262169</v>
+        <v>122262149</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>90809</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,31 +1272,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1311,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568766</v>
+        <v>568834</v>
       </c>
       <c r="R7" t="n">
-        <v>6434978</v>
+        <v>6434943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,6 +1351,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262138</v>
+        <v>122262169</v>
       </c>
       <c r="B8" t="n">
-        <v>94850</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,31 +1382,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568911</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434976</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1462,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262123</v>
+        <v>122262266</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,20 +1492,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,23 +1518,23 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568908</v>
+        <v>568766</v>
       </c>
       <c r="R9" t="n">
-        <v>6434963</v>
+        <v>6434978</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>122231767</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262138</v>
+        <v>122262169</v>
       </c>
       <c r="B5" t="n">
-        <v>94850</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1051,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568911</v>
+        <v>568766</v>
       </c>
       <c r="R5" t="n">
-        <v>6434976</v>
+        <v>6434978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,7 +1152,7 @@
         <v>122262123</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262149</v>
+        <v>122262138</v>
       </c>
       <c r="B7" t="n">
-        <v>90809</v>
+        <v>94862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1271,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568834</v>
+        <v>568911</v>
       </c>
       <c r="R7" t="n">
-        <v>6434943</v>
+        <v>6434976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262169</v>
+        <v>122262149</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>90821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1382,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568766</v>
+        <v>568834</v>
       </c>
       <c r="R8" t="n">
-        <v>6434978</v>
+        <v>6434943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,6 +1461,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>122262266</v>
       </c>
       <c r="B9" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262169</v>
+        <v>122262149</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>90828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,31 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568766</v>
+        <v>568834</v>
       </c>
       <c r="R5" t="n">
-        <v>6434978</v>
+        <v>6434943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262123</v>
+        <v>122262169</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1193,14 +1197,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568908</v>
+        <v>568766</v>
       </c>
       <c r="R6" t="n">
-        <v>6434963</v>
+        <v>6434978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1266,7 @@
         <v>122262138</v>
       </c>
       <c r="B7" t="n">
-        <v>94862</v>
+        <v>94867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262149</v>
+        <v>122262266</v>
       </c>
       <c r="B8" t="n">
-        <v>90821</v>
+        <v>57749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1382,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1462,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262266</v>
+        <v>122262123</v>
       </c>
       <c r="B9" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,20 +1492,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,23 +1518,23 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R9" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -929,11 +929,6 @@
       <c r="E4" t="n">
         <v>103021</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -1039,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262149</v>
+        <v>122262266</v>
       </c>
       <c r="B5" t="n">
-        <v>90828</v>
+        <v>57749</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1046,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R5" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1121,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262169</v>
+        <v>122262123</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1170,11 +1156,6 @@
       </c>
       <c r="E6" t="n">
         <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1197,14 +1178,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R6" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262138</v>
+        <v>122262149</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,31 +1256,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568911</v>
+        <v>568834</v>
       </c>
       <c r="R7" t="n">
-        <v>6434976</v>
+        <v>6434943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262266</v>
+        <v>122262138</v>
       </c>
       <c r="B8" t="n">
-        <v>57749</v>
+        <v>94876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1369,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>2170</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R8" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262123</v>
+        <v>122262169</v>
       </c>
       <c r="B9" t="n">
         <v>57395</v>
@@ -1497,11 +1472,6 @@
       </c>
       <c r="E9" t="n">
         <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1524,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568908</v>
+        <v>568766</v>
       </c>
       <c r="R9" t="n">
-        <v>6434963</v>
+        <v>6434978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>122231767</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,6 +928,11 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1034,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262266</v>
+        <v>122262169</v>
       </c>
       <c r="B5" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,15 +1051,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,7 +1077,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1083,7 +1093,7 @@
         <v>6434978</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262123</v>
+        <v>122262138</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>94889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,41 +1161,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2170</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568908</v>
+        <v>568911</v>
       </c>
       <c r="R6" t="n">
-        <v>6434963</v>
+        <v>6434976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,6 +1237,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262149</v>
+        <v>122262123</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,40 +1272,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568834</v>
+        <v>568908</v>
       </c>
       <c r="R7" t="n">
-        <v>6434943</v>
+        <v>6434963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1348,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262138</v>
+        <v>122262266</v>
       </c>
       <c r="B8" t="n">
-        <v>94876</v>
+        <v>57753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,22 +1382,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,13 +1414,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568911</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434976</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1458,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262169</v>
+        <v>122262149</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>90846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,26 +1492,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568766</v>
+        <v>568834</v>
       </c>
       <c r="R9" t="n">
-        <v>6434978</v>
+        <v>6434943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,6 +1571,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262169</v>
+        <v>122262266</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,20 +1051,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
         <v>6434978</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>122262138</v>
       </c>
       <c r="B6" t="n">
-        <v>94889</v>
+        <v>94902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262123</v>
+        <v>122262149</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>90859</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,42 +1272,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568908</v>
+        <v>568834</v>
       </c>
       <c r="R7" t="n">
-        <v>6434963</v>
+        <v>6434943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,6 +1351,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1366,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262266</v>
+        <v>122262123</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,20 +1382,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1404,23 +1408,23 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R8" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262149</v>
+        <v>122262169</v>
       </c>
       <c r="B9" t="n">
-        <v>90846</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,34 +1496,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1527,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R9" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1572,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262266</v>
+        <v>122262138</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>94902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,31 +1055,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R5" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,6 +1127,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262138</v>
+        <v>122262123</v>
       </c>
       <c r="B6" t="n">
-        <v>94902</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,42 +1158,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568911</v>
+        <v>568908</v>
       </c>
       <c r="R6" t="n">
-        <v>6434976</v>
+        <v>6434963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1238,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262149</v>
+        <v>122262266</v>
       </c>
       <c r="B7" t="n">
-        <v>90859</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1268,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R7" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1348,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262123</v>
+        <v>122262149</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>90859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,42 +1382,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568908</v>
+        <v>568834</v>
       </c>
       <c r="R8" t="n">
-        <v>6434963</v>
+        <v>6434943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,6 +1461,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>122262138</v>
       </c>
       <c r="B5" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262123</v>
+        <v>122262149</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>90853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,42 +1162,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568908</v>
+        <v>568834</v>
       </c>
       <c r="R6" t="n">
-        <v>6434963</v>
+        <v>6434943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262266</v>
+        <v>122262123</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,20 +1272,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,23 +1298,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R7" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262149</v>
+        <v>122262169</v>
       </c>
       <c r="B8" t="n">
-        <v>90859</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1386,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1462,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262169</v>
+        <v>122262266</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,20 +1492,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,7 +1518,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>6434978</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262138</v>
+        <v>122262169</v>
       </c>
       <c r="B5" t="n">
-        <v>94904</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1051,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568911</v>
+        <v>568766</v>
       </c>
       <c r="R5" t="n">
-        <v>6434976</v>
+        <v>6434978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262169</v>
+        <v>122262138</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>94904</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,35 +1385,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R8" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,6 +1461,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122262169</v>
+        <v>122262123</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,14 +1083,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568766</v>
+        <v>568908</v>
       </c>
       <c r="R5" t="n">
-        <v>6434978</v>
+        <v>6434963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122262149</v>
+        <v>122262169</v>
       </c>
       <c r="B6" t="n">
-        <v>90853</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,34 +1165,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568834</v>
+        <v>568766</v>
       </c>
       <c r="R6" t="n">
-        <v>6434943</v>
+        <v>6434978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1241,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1263,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262123</v>
+        <v>122262149</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,42 +1275,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568908</v>
+        <v>568834</v>
       </c>
       <c r="R7" t="n">
-        <v>6434963</v>
+        <v>6434943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,6 +1354,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122262138</v>
+        <v>122262266</v>
       </c>
       <c r="B8" t="n">
-        <v>94904</v>
+        <v>57754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,27 +1389,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568911</v>
+        <v>568766</v>
       </c>
       <c r="R8" t="n">
-        <v>6434976</v>
+        <v>6434978</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262266</v>
+        <v>122262138</v>
       </c>
       <c r="B9" t="n">
-        <v>57753</v>
+        <v>94905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,31 +1499,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1528,13 +1527,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568766</v>
+        <v>568911</v>
       </c>
       <c r="R9" t="n">
-        <v>6434978</v>
+        <v>6434976</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,6 +1571,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,6 +1588,122 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128131137</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568828</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6434948</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>128131137</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>128131137</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>128131137</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">

--- a/artfynd/A 59457-2024 artfynd.xlsx
+++ b/artfynd/A 59457-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121699106</v>
+        <v>122262138</v>
       </c>
       <c r="B2" t="n">
-        <v>97103</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568829</v>
+        <v>568911</v>
       </c>
       <c r="R2" t="n">
-        <v>6434927</v>
+        <v>6434976</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,34 +744,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett större område men fler mindre i direkt närhet.</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -793,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -808,12 +780,7 @@
         <v>121713395</v>
       </c>
       <c r="B3" t="n">
-        <v>94921</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122231767</v>
+        <v>122262149</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,31 +911,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pjäkebo sumpskogen , Sm</t>
+          <t>A 59427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568829</v>
+        <v>568834</v>
       </c>
       <c r="R4" t="n">
-        <v>6434927</v>
+        <v>6434943</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,18 +968,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,16 +990,11 @@
         <v>122262123</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1152,16 +1095,11 @@
         <v>122262169</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1259,37 +1197,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122262149</v>
+        <v>128131137</v>
       </c>
       <c r="B7" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1297,23 +1230,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568834</v>
+        <v>568828</v>
       </c>
       <c r="R7" t="n">
-        <v>6434943</v>
+        <v>6434948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,12 +1271,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,19 +1295,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1376,12 +1316,7 @@
         <v>122262266</v>
       </c>
       <c r="B8" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,57 +1418,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122262138</v>
+        <v>122231767</v>
       </c>
       <c r="B9" t="n">
-        <v>94905</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59427, Pjäkebo, Sm</t>
+          <t>Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568911</v>
+        <v>568829</v>
       </c>
       <c r="R9" t="n">
-        <v>6434976</v>
+        <v>6434927</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,90 +1499,102 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128131137</v>
+        <v>121699106</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pjäkebo sumpskogen , Pjäkebo sumpskogen , Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568828</v>
+        <v>568829</v>
       </c>
       <c r="R10" t="n">
-        <v>6434948</v>
+        <v>6434927</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,22 +1618,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett större område men fler mindre i direkt närhet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,6 +1647,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
